--- a/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点19.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点19.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\Tb-云量50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FA7C1C-9125-4994-9B62-4822FC56237A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84FF81C-2944-45EA-B7A3-A571EB0FF0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00000000000"/>
+    <numFmt numFmtId="176" formatCode="0.00000000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -130,7 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2353,7 +2353,7 @@
         <v>202311</v>
       </c>
       <c r="B98" s="4">
-        <v>114.659195324</v>
+        <v>93.466969741400007</v>
       </c>
       <c r="C98">
         <v>3.532</v>
@@ -2370,7 +2370,7 @@
         <v>202312</v>
       </c>
       <c r="B99" s="4">
-        <v>77.305766642699993</v>
+        <v>22.292794595099998</v>
       </c>
       <c r="C99">
         <v>4.1360000000000001</v>
